--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16955</v>
+        <v>16.77769</v>
       </c>
       <c r="D2" t="n">
-        <v>16.85847</v>
+        <v>16.77301</v>
       </c>
       <c r="E2" t="n">
-        <v>16.90097</v>
+        <v>16.77603</v>
       </c>
       <c r="F2" t="n">
-        <v>42.55393</v>
+        <v>43.76871</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05158</v>
+        <v>0.05051</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84577</v>
+        <v>1.83005</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.14341</v>
+        <v>16.85037</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63783</v>
+        <v>16.80106</v>
       </c>
       <c r="E3" t="n">
-        <v>16.88668</v>
+        <v>16.81246</v>
       </c>
       <c r="F3" t="n">
-        <v>43.32443</v>
+        <v>42.24726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05082</v>
+        <v>0.05052</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84132</v>
+        <v>1.82968</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.08059</v>
+        <v>16.95767</v>
       </c>
       <c r="D4" t="n">
-        <v>16.45669</v>
+        <v>16.64599</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72595</v>
+        <v>16.94231</v>
       </c>
       <c r="F4" t="n">
-        <v>42.88596</v>
+        <v>42.90018</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05189</v>
+        <v>0.05062</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83244</v>
+        <v>1.82017</v>
       </c>
     </row>
   </sheetData>
